--- a/final_results/models_trained_on_all_datasets_averaged_by_organ.xlsx
+++ b/final_results/models_trained_on_all_datasets_averaged_by_organ.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mkkad\Desktop\github_repos\medical-segmentation-calibration-ood\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mkkad\Desktop\github_repos\medical-segmentation-calibration-ood\final_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0960D3B8-DCD2-4CD9-A2DD-9B7673681E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEAF57F3-65F1-444F-9CFF-326D2723A431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="36">
   <si>
     <t>kidney</t>
   </si>
@@ -145,6 +145,9 @@
   </si>
   <si>
     <t>Parameter</t>
+  </si>
+  <si>
+    <t>DCS (Multi-task learning)</t>
   </si>
 </sst>
 </file>
@@ -226,23 +229,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -251,23 +247,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1287,18 +1286,18 @@
   <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>27</v>
       </c>
       <c r="M1" s="3" t="s">
@@ -1306,14 +1305,14 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="12" t="s">
         <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" s="2">
-        <f>M2*100</f>
+        <f t="shared" ref="C2:C25" si="0">M2*100</f>
         <v>99.588009595870972</v>
       </c>
       <c r="M2">
@@ -1321,12 +1320,12 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
+      <c r="A3" s="12"/>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="2">
-        <f>M3*100</f>
+        <f t="shared" si="0"/>
         <v>99.509807676076889</v>
       </c>
       <c r="M3">
@@ -1334,12 +1333,12 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
+      <c r="A4" s="12"/>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="2">
-        <f>M4*100</f>
+        <f t="shared" si="0"/>
         <v>99.197131493860041</v>
       </c>
       <c r="M4">
@@ -1347,12 +1346,12 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
+      <c r="A5" s="12"/>
       <c r="B5" t="s">
         <v>3</v>
       </c>
       <c r="C5" s="2">
-        <f>M5*100</f>
+        <f t="shared" si="0"/>
         <v>99.950135957736236</v>
       </c>
       <c r="M5">
@@ -1360,12 +1359,12 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
+      <c r="A6" s="12"/>
       <c r="B6" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="2">
-        <f>M6*100</f>
+        <f t="shared" si="0"/>
         <v>98.057573891821363</v>
       </c>
       <c r="M6">
@@ -1373,12 +1372,12 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
+      <c r="A7" s="12"/>
       <c r="B7" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="2">
-        <f>M7*100</f>
+        <f t="shared" si="0"/>
         <v>99.160295724868774</v>
       </c>
       <c r="M7">
@@ -1386,12 +1385,12 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
+      <c r="A8" s="12"/>
       <c r="B8" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="2">
-        <f>M8*100</f>
+        <f t="shared" si="0"/>
         <v>99.647028923034668</v>
       </c>
       <c r="M8">
@@ -1399,12 +1398,12 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
+      <c r="A9" s="12"/>
       <c r="B9" t="s">
         <v>21</v>
       </c>
       <c r="C9" s="2">
-        <f>M9*100</f>
+        <f t="shared" si="0"/>
         <v>99.829206934997018</v>
       </c>
       <c r="M9">
@@ -1412,14 +1411,14 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="12" t="s">
         <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="2">
-        <f>M10*100</f>
+        <f t="shared" si="0"/>
         <v>98.833034515380859</v>
       </c>
       <c r="M10">
@@ -1427,12 +1426,12 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
+      <c r="A11" s="12"/>
       <c r="B11" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="2">
-        <f>M11*100</f>
+        <f t="shared" si="0"/>
         <v>97.224900871515274</v>
       </c>
       <c r="M11">
@@ -1440,12 +1439,12 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
+      <c r="A12" s="12"/>
       <c r="B12" t="s">
         <v>22</v>
       </c>
       <c r="C12" s="2">
-        <f>M12*100</f>
+        <f t="shared" si="0"/>
         <v>98.922951605694351</v>
       </c>
       <c r="M12">
@@ -1453,12 +1452,12 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
+      <c r="A13" s="12"/>
       <c r="B13" t="s">
         <v>3</v>
       </c>
       <c r="C13" s="2">
-        <f>M13*100</f>
+        <f t="shared" si="0"/>
         <v>99.96948895546106</v>
       </c>
       <c r="M13">
@@ -1466,12 +1465,12 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
+      <c r="A14" s="12"/>
       <c r="B14" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="2">
-        <f>M14*100</f>
+        <f t="shared" si="0"/>
         <v>96.727768225329257</v>
       </c>
       <c r="M14">
@@ -1479,12 +1478,12 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
+      <c r="A15" s="12"/>
       <c r="B15" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="2">
-        <f>M15*100</f>
+        <f t="shared" si="0"/>
         <v>99.341542273759842</v>
       </c>
       <c r="M15">
@@ -1492,12 +1491,12 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
+      <c r="A16" s="12"/>
       <c r="B16" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="2">
-        <f>M16*100</f>
+        <f t="shared" si="0"/>
         <v>97.905152797698975</v>
       </c>
       <c r="M16">
@@ -1505,12 +1504,12 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
+      <c r="A17" s="12"/>
       <c r="B17" t="s">
         <v>21</v>
       </c>
       <c r="C17" s="2">
-        <f>M17*100</f>
+        <f t="shared" si="0"/>
         <v>99.478502465145922</v>
       </c>
       <c r="M17">
@@ -1518,14 +1517,14 @@
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="12" t="s">
         <v>14</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="2">
-        <f>M18*100</f>
+        <f t="shared" si="0"/>
         <v>80.323452115058899</v>
       </c>
       <c r="M18">
@@ -1533,12 +1532,12 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
+      <c r="A19" s="12"/>
       <c r="B19" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="2">
-        <f>M19*100</f>
+        <f t="shared" si="0"/>
         <v>79.837141931056976</v>
       </c>
       <c r="M19">
@@ -1546,12 +1545,12 @@
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
+      <c r="A20" s="12"/>
       <c r="B20" t="s">
         <v>22</v>
       </c>
       <c r="C20" s="2">
-        <f>M20*100</f>
+        <f t="shared" si="0"/>
         <v>88.285174596408183</v>
       </c>
       <c r="M20">
@@ -1559,12 +1558,12 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
+      <c r="A21" s="12"/>
       <c r="B21" t="s">
         <v>3</v>
       </c>
       <c r="C21" s="2">
-        <f>M21*100</f>
+        <f t="shared" si="0"/>
         <v>78.284532003677811</v>
       </c>
       <c r="M21">
@@ -1572,12 +1571,12 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
+      <c r="A22" s="12"/>
       <c r="B22" t="s">
         <v>17</v>
       </c>
       <c r="C22" s="2">
-        <f>M22*100</f>
+        <f t="shared" si="0"/>
         <v>78.373995707148609</v>
       </c>
       <c r="M22">
@@ -1585,12 +1584,12 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
+      <c r="A23" s="12"/>
       <c r="B23" t="s">
         <v>18</v>
       </c>
       <c r="C23" s="2">
-        <f>M23*100</f>
+        <f t="shared" si="0"/>
         <v>78.210671246051788</v>
       </c>
       <c r="M23">
@@ -1598,12 +1597,12 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
+      <c r="A24" s="12"/>
       <c r="B24" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="2">
-        <f>M24*100</f>
+        <f t="shared" si="0"/>
         <v>80.036463737487793</v>
       </c>
       <c r="M24">
@@ -1611,12 +1610,12 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
+      <c r="A25" s="12"/>
       <c r="B25" t="s">
         <v>21</v>
       </c>
       <c r="C25" s="2">
-        <f>M25*100</f>
+        <f t="shared" si="0"/>
         <v>79.955087868230677</v>
       </c>
       <c r="M25">
@@ -1655,7 +1654,7 @@
       <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="7" t="s">
         <v>28</v>
       </c>
       <c r="L1" s="1" t="s">
@@ -1663,14 +1662,14 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="13" t="s">
         <v>12</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" s="2">
-        <f>L2*100</f>
+        <f t="shared" ref="C2:C25" si="0">L2*100</f>
         <v>97.440188744711492</v>
       </c>
       <c r="L2">
@@ -1678,12 +1677,12 @@
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
+      <c r="A3" s="11"/>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" s="2">
-        <f>L3*100</f>
+        <f t="shared" si="0"/>
         <v>99.405782421429961</v>
       </c>
       <c r="L3">
@@ -1691,12 +1690,12 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
+      <c r="A4" s="11"/>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="2">
-        <f>L4*100</f>
+        <f t="shared" si="0"/>
         <v>99.54045017560324</v>
       </c>
       <c r="L4">
@@ -1704,12 +1703,12 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
+      <c r="A5" s="11"/>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" s="2">
-        <f>L5*100</f>
+        <f t="shared" si="0"/>
         <v>99.948998445119614</v>
       </c>
       <c r="L5">
@@ -1717,12 +1716,12 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
+      <c r="A6" s="11"/>
       <c r="B6" t="s">
         <v>17</v>
       </c>
       <c r="C6" s="2">
-        <f>L6*100</f>
+        <f t="shared" si="0"/>
         <v>99.701233373747939</v>
       </c>
       <c r="L6">
@@ -1730,12 +1729,12 @@
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
+      <c r="A7" s="11"/>
       <c r="B7" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="2">
-        <f>L7*100</f>
+        <f t="shared" si="0"/>
         <v>99.815227517059867</v>
       </c>
       <c r="L7">
@@ -1743,12 +1742,12 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
+      <c r="A8" s="11"/>
       <c r="B8" t="s">
         <v>20</v>
       </c>
       <c r="C8" s="2">
-        <f>L8*100</f>
+        <f t="shared" si="0"/>
         <v>99.241997467146987</v>
       </c>
       <c r="L8">
@@ -1756,12 +1755,12 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
+      <c r="A9" s="11"/>
       <c r="B9" t="s">
         <v>21</v>
       </c>
       <c r="C9" s="2">
-        <f>L9*100</f>
+        <f t="shared" si="0"/>
         <v>99.595714904166556</v>
       </c>
       <c r="L9">
@@ -1769,14 +1768,14 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="11" t="s">
         <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="2">
-        <f>L10*100</f>
+        <f t="shared" si="0"/>
         <v>96.114333281441347</v>
       </c>
       <c r="L10">
@@ -1784,12 +1783,12 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
+      <c r="A11" s="11"/>
       <c r="B11" t="s">
         <v>19</v>
       </c>
       <c r="C11" s="2">
-        <f>L11*100</f>
+        <f t="shared" si="0"/>
         <v>99.338068564732879</v>
       </c>
       <c r="L11">
@@ -1797,12 +1796,12 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
+      <c r="A12" s="11"/>
       <c r="B12" t="s">
         <v>22</v>
       </c>
       <c r="C12" s="2">
-        <f>L12*100</f>
+        <f t="shared" si="0"/>
         <v>96.931352217992156</v>
       </c>
       <c r="L12">
@@ -1810,12 +1809,12 @@
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
+      <c r="A13" s="11"/>
       <c r="B13" t="s">
         <v>26</v>
       </c>
       <c r="C13" s="2">
-        <f>L13*100</f>
+        <f t="shared" si="0"/>
         <v>99.96923124178862</v>
       </c>
       <c r="L13">
@@ -1823,12 +1822,12 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
+      <c r="A14" s="11"/>
       <c r="B14" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="2">
-        <f>L14*100</f>
+        <f t="shared" si="0"/>
         <v>98.699307110574509</v>
       </c>
       <c r="L14">
@@ -1836,12 +1835,12 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
+      <c r="A15" s="11"/>
       <c r="B15" t="s">
         <v>18</v>
       </c>
       <c r="C15" s="2">
-        <f>L15*100</f>
+        <f t="shared" si="0"/>
         <v>99.581754988148091</v>
       </c>
       <c r="L15">
@@ -1849,12 +1848,12 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
+      <c r="A16" s="11"/>
       <c r="B16" t="s">
         <v>20</v>
       </c>
       <c r="C16" s="2">
-        <f>L16*100</f>
+        <f t="shared" si="0"/>
         <v>98.9795669582155</v>
       </c>
       <c r="L16">
@@ -1862,12 +1861,12 @@
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
+      <c r="A17" s="11"/>
       <c r="B17" t="s">
         <v>21</v>
       </c>
       <c r="C17" s="2">
-        <f>L17*100</f>
+        <f t="shared" si="0"/>
         <v>98.878433414407681</v>
       </c>
       <c r="L17">
@@ -1875,14 +1874,14 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="11" t="s">
         <v>14</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="2">
-        <f>L18*100</f>
+        <f t="shared" si="0"/>
         <v>78.410340017742584</v>
       </c>
       <c r="L18">
@@ -1890,12 +1889,12 @@
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
+      <c r="A19" s="11"/>
       <c r="B19" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="2">
-        <f>L19*100</f>
+        <f t="shared" si="0"/>
         <v>78.374321262041718</v>
       </c>
       <c r="L19">
@@ -1903,12 +1902,12 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="6"/>
+      <c r="A20" s="11"/>
       <c r="B20" t="s">
         <v>22</v>
       </c>
       <c r="C20" s="2">
-        <f>L20*100</f>
+        <f t="shared" si="0"/>
         <v>80.052255590756744</v>
       </c>
       <c r="L20">
@@ -1916,12 +1915,12 @@
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
+      <c r="A21" s="11"/>
       <c r="B21" t="s">
         <v>26</v>
       </c>
       <c r="C21" s="2">
-        <f>L21*100</f>
+        <f t="shared" si="0"/>
         <v>78.298159822439544</v>
       </c>
       <c r="L21">
@@ -1929,12 +1928,12 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
+      <c r="A22" s="11"/>
       <c r="B22" t="s">
         <v>17</v>
       </c>
       <c r="C22" s="2">
-        <f>L22*100</f>
+        <f t="shared" si="0"/>
         <v>80.913830134603714</v>
       </c>
       <c r="L22">
@@ -1942,12 +1941,12 @@
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
+      <c r="A23" s="11"/>
       <c r="B23" t="s">
         <v>18</v>
       </c>
       <c r="C23" s="2">
-        <f>L23*100</f>
+        <f t="shared" si="0"/>
         <v>79.903364039602735</v>
       </c>
       <c r="L23">
@@ -1955,12 +1954,12 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
+      <c r="A24" s="11"/>
       <c r="B24" t="s">
         <v>20</v>
       </c>
       <c r="C24" s="2">
-        <f>L24*100</f>
+        <f t="shared" si="0"/>
         <v>88.083321783277725</v>
       </c>
       <c r="L24">
@@ -1968,12 +1967,12 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
+      <c r="A25" s="11"/>
       <c r="B25" t="s">
         <v>21</v>
       </c>
       <c r="C25" s="2">
-        <f>L25*100</f>
+        <f t="shared" si="0"/>
         <v>80.289389152784608</v>
       </c>
       <c r="L25">
@@ -2006,88 +2005,88 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="16"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
+      <c r="D1" s="14"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="6"/>
-      <c r="K2" s="9" t="s">
+      <c r="D2" s="11"/>
+      <c r="K2" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
+      <c r="L2" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
     </row>
     <row r="3" spans="1:17" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
       <c r="C3" t="s">
         <v>16</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="14" t="s">
+      <c r="M3" s="12"/>
+      <c r="N3" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="14"/>
-      <c r="P3" s="8" t="s">
+      <c r="O3" s="10"/>
+      <c r="P3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="Q3" s="8"/>
+      <c r="Q3" s="12"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="K4" s="9" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="K4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="N4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O4" s="9" t="s">
+      <c r="O4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="9" t="s">
+      <c r="P4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="Q4" s="9" t="s">
+      <c r="Q4" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="12" t="s">
         <v>12</v>
       </c>
       <c r="B5" t="s">
@@ -2122,7 +2121,7 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
+      <c r="A6" s="12"/>
       <c r="B6" t="s">
         <v>19</v>
       </c>
@@ -2155,7 +2154,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
+      <c r="A7" s="12"/>
       <c r="B7" t="s">
         <v>22</v>
       </c>
@@ -2188,7 +2187,7 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
+      <c r="A8" s="12"/>
       <c r="B8" t="s">
         <v>3</v>
       </c>
@@ -2221,7 +2220,7 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
+      <c r="A9" s="12"/>
       <c r="B9" t="s">
         <v>17</v>
       </c>
@@ -2254,7 +2253,7 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
+      <c r="A10" s="12"/>
       <c r="B10" t="s">
         <v>18</v>
       </c>
@@ -2287,7 +2286,7 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
+      <c r="A11" s="12"/>
       <c r="B11" t="s">
         <v>20</v>
       </c>
@@ -2320,7 +2319,7 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
+      <c r="A12" s="12"/>
       <c r="B12" t="s">
         <v>21</v>
       </c>
@@ -2353,7 +2352,7 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="12" t="s">
         <v>13</v>
       </c>
       <c r="B13" t="s">
@@ -2367,7 +2366,7 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
+      <c r="A14" s="12"/>
       <c r="B14" t="s">
         <v>19</v>
       </c>
@@ -2379,7 +2378,7 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
+      <c r="A15" s="12"/>
       <c r="B15" t="s">
         <v>22</v>
       </c>
@@ -2391,7 +2390,7 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
+      <c r="A16" s="12"/>
       <c r="B16" t="s">
         <v>3</v>
       </c>
@@ -2403,7 +2402,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
+      <c r="A17" s="12"/>
       <c r="B17" t="s">
         <v>17</v>
       </c>
@@ -2415,7 +2414,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
+      <c r="A18" s="12"/>
       <c r="B18" t="s">
         <v>18</v>
       </c>
@@ -2427,7 +2426,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
+      <c r="A19" s="12"/>
       <c r="B19" t="s">
         <v>20</v>
       </c>
@@ -2439,7 +2438,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
+      <c r="A20" s="12"/>
       <c r="B20" t="s">
         <v>21</v>
       </c>
@@ -2451,7 +2450,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="12" t="s">
         <v>14</v>
       </c>
       <c r="B21" t="s">
@@ -2465,7 +2464,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
+      <c r="A22" s="12"/>
       <c r="B22" t="s">
         <v>19</v>
       </c>
@@ -2477,7 +2476,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
+      <c r="A23" s="12"/>
       <c r="B23" t="s">
         <v>22</v>
       </c>
@@ -2489,7 +2488,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
+      <c r="A24" s="12"/>
       <c r="B24" t="s">
         <v>3</v>
       </c>
@@ -2501,7 +2500,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
+      <c r="A25" s="12"/>
       <c r="B25" t="s">
         <v>17</v>
       </c>
@@ -2513,7 +2512,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
+      <c r="A26" s="12"/>
       <c r="B26" t="s">
         <v>18</v>
       </c>
@@ -2525,7 +2524,7 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
+      <c r="A27" s="12"/>
       <c r="B27" t="s">
         <v>20</v>
       </c>
@@ -2537,7 +2536,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
+      <c r="A28" s="12"/>
       <c r="B28" t="s">
         <v>21</v>
       </c>
@@ -2550,11 +2549,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A13:A20"/>
     <mergeCell ref="A21:A28"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="L1:M1"/>
@@ -2562,6 +2556,11 @@
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A5:A12"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="A13:A20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2577,49 +2576,49 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="14" t="s">
+      <c r="A3" s="12"/>
+      <c r="B3" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14" t="s">
+      <c r="C3" s="10"/>
+      <c r="D3" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="E3" s="14"/>
-      <c r="G3" s="12"/>
-      <c r="H3" s="12"/>
+      <c r="E3" s="10"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
     </row>
     <row r="4" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="15" t="s">
+      <c r="A4" s="12"/>
+      <c r="B4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -2632,8 +2631,8 @@
       <c r="D5" s="2">
         <v>97.21</v>
       </c>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -2651,8 +2650,8 @@
       <c r="E6" s="2">
         <v>89</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -2665,8 +2664,8 @@
       <c r="D7" s="2">
         <v>97.98</v>
       </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -2684,8 +2683,8 @@
       <c r="E8" s="2">
         <v>88</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -2703,8 +2702,8 @@
       <c r="E9" s="2">
         <v>91</v>
       </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -2722,8 +2721,8 @@
       <c r="E10" s="2">
         <v>96</v>
       </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -2736,8 +2735,8 @@
       <c r="D11" s="2">
         <v>99.89</v>
       </c>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -2755,8 +2754,8 @@
       <c r="E12" s="2">
         <v>80</v>
       </c>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
